--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -468,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1990</v>
+        <v>1748</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-119</v>
+        <v>125</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>40</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1551</v>
+        <v>1662</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1748</v>
+        <v>1537</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-197</v>
+        <v>125</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1851</v>
+        <v>1662</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1748</v>
+        <v>1537</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -653,7 +653,7 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,28 +677,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1021</v>
+        <v>1662</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>918</v>
+        <v>1537</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>921</v>
+        <v>1153</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>918</v>
+        <v>1014</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>40</v>
@@ -743,7 +743,7 @@
       <c r="I6" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,26 +771,26 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>843</v>
+        <v>2094</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-12</v>
+        <v>-1255</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1101</v>
+        <v>923</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1014</v>
+        <v>918</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>40</v>
@@ -833,282 +833,12 @@
       <c r="I8" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>03-JUL-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1101</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1128</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-27</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1101</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1014</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>721</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>07-AUG-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>671</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>671</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-247</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>671</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-247</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -549,10 +558,10 @@
         <v>1873</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1748</v>
+        <v>1990</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>125</v>
+        <v>-117</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>40</v>
@@ -565,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -608,7 +617,7 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -653,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -681,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1662</v>
+        <v>1501</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1537</v>
+        <v>1358</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -698,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,26 +735,26 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1153</v>
+        <v>839</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1014</v>
+        <v>2094</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>139</v>
+        <v>-1255</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,26 +780,26 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>839</v>
+        <v>923</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2094</v>
+        <v>918</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1255</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>923</v>
+        <v>673</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>40</v>
@@ -833,12 +842,57 @@
       <c r="I8" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>flyadeal F3-753</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1873</v>
+        <v>809</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1990</v>
+        <v>2094</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-117</v>
+        <v>-1285</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1662</v>
+        <v>861</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1537</v>
+        <v>2094</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>125</v>
+        <v>-1233</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>flyadeal F3-761</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1662</v>
+        <v>889</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1537</v>
+        <v>2094</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>125</v>
+        <v>-1205</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>flynas XY-573</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1501</v>
+        <v>911</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1358</v>
+        <v>2094</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>143</v>
+        <v>-1183</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>839</v>
+        <v>938</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>2094</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1255</v>
+        <v>-1156</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>918</v>
+        <v>2094</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5</v>
+        <v>-1156</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>673</v>
+        <v>938</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>648</v>
+        <v>2094</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>25</v>
+        <v>-1156</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,33 +866,8808 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>EgyptAir MS-660</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>995</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-1099</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>995</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-1099</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-1083</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-1083</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-1051</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-1049</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-933</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-933</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-933</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-3261</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-933</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-933</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-741</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-303</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-741</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-741</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-741</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-335</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1427</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-667</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-321</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1538</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-556</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-642</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-356</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>20-MAY-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-356</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-573</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-979</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-979</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-947</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-947</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-931</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-931</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-931</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-829</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-829</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-829</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-829</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-829</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-627</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-627</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-570</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1488</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-502</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-660</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1488</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-502</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>22-MAY-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1488</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-502</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-648</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-648</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-648</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-573</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-326</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-527</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-526</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-494</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1138</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-646</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1248</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-289</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-642</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>1371</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-166</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-117</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>23-MAY-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8224</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1662</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-788</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-728</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-728</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-573</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-604</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-602</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1138</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-646</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1138</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1138</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-660</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1138</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1195</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-342</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-642</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1363</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1476</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-61</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8224</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1662</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-609</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-609</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-609</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-549</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-527</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-527</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-527</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-524</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-523</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-423</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-408</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>995</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-363</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>26-MAY-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8224</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1501</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-515</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-515</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-515</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>590</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-424</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-413</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-413</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>615</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-573</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-373</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-642</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>-281</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>-317</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>-317</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>601</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>-317</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>636</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>-282</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>-277</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>-207</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>-207</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-207</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>29-MAY-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>711</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-207</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-1405</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-1263</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-1263</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>-1263</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
           <t>flynas XY-581</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>673</v>
-      </c>
-      <c r="E9" s="2" t="n">
+      <c r="D136" s="2" t="n">
+        <v>839</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>-1255</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>-1176</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>-1176</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-1176</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-335</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>-1176</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>-1161</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>-1051</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>-1049</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>-1035</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>-1035</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>-1035</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-328</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>-993</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-112</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>-786</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-160</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>-786</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-110</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>-786</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-162</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-786</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>-774</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>-759</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-132</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>1458</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>-636</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-148</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1498</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>-596</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-126</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1498</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>-596</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-130</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1498</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>-596</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>639</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>-489</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>-439</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>-377</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>-297</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>-297</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>05-JUN-26</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>-297</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>-275</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>-222</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>-222</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-303</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>-153</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>13-JUN-26</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-656</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>-171</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>-281</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>791</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>-171</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>-281</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>-281</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>-231</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>723</v>
+      </c>
+      <c r="E186" s="2" t="n">
         <v>648</v>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" s="2" t="n">
+      <c r="F186" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G186" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
+      <c r="H186" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I186" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J186" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>-529</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-753</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>-529</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-763</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>-529</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-761</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>-529</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-583</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-567</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-589</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>-417</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1253</v>
+        <v>909</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-105</v>
+        <v>-449</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,28 +596,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-573</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1280</v>
+        <v>1363</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-78</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1501</v>
+        <v>1363</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>143</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1168</v>
+        <v>1501</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>987</v>
+        <v>1358</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>745</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1085</v>
+        <v>1210</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-340</v>
+        <v>-465</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>938</v>
+        <v>745</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1085</v>
+        <v>1210</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-147</v>
+        <v>-465</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -828,10 +828,10 @@
         <v>995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1085</v>
+        <v>1210</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-90</v>
+        <v>-215</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1256</v>
+        <v>1368</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1085</v>
+        <v>1210</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>733</v>
+        <v>590</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-185</v>
+        <v>-328</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>783</v>
+        <v>733</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-135</v>
+        <v>-185</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1022,7 +1022,7 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>flyadeal F3-763</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>745</v>
+        <v>709</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2094</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1349</v>
+        <v>-1385</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>745</v>
+        <v>834</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>2094</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1349</v>
+        <v>-1260</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>2094</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1263</v>
+        <v>-1260</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1208,186 +1208,6 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>833</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>768</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-644</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>554</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>768</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-646</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>554</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>768</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-666</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>554</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>768</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>flynas XY-583</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>909</v>
+        <v>1253</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-449</v>
+        <v>-105</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1363</v>
+        <v>1253</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>-105</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>flynas XY-577</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1363</v>
+        <v>1253</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>-105</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>745</v>
+        <v>1248</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-465</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>745</v>
+        <v>1253</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-465</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>995</v>
+        <v>1368</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-215</v>
+        <v>158</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1368</v>
+        <v>834</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>158</v>
+        <v>-376</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>590</v>
+        <v>995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>918</v>
+        <v>1210</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-328</v>
+        <v>-215</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>733</v>
+        <v>1033</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>918</v>
+        <v>1210</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-185</v>
+        <v>-177</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>783</v>
+        <v>1368</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>918</v>
+        <v>1210</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-135</v>
+        <v>158</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>609</v>
+        <v>783</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2094</v>
+        <v>918</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1485</v>
+        <v>-135</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-763</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>709</v>
+        <v>783</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2094</v>
+        <v>918</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1385</v>
+        <v>-135</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>834</v>
+        <v>783</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2094</v>
+        <v>918</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1260</v>
+        <v>-135</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,43 +1171,403 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>27-MAY-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>943</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>03-JUN-26</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-128</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-173</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-171</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>793</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2094</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-1301</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>03-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-228</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
         <v>834</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>2094</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>-1260</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-249</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-646</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-583</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1253</v>
+        <v>1363</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-105</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1253</v>
+        <v>1363</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-105</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-577</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1253</v>
+        <v>1501</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-105</v>
+        <v>143</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1501</v>
+        <v>1248</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1358</v>
+        <v>1210</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1248</v>
+        <v>1368</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1253</v>
+        <v>834</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1210</v>
+        <v>1085</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43</v>
+        <v>-251</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1368</v>
+        <v>835</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1210</v>
+        <v>1085</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>158</v>
+        <v>-250</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>834</v>
+        <v>995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1210</v>
+        <v>1085</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-376</v>
+        <v>-90</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>995</v>
+        <v>783</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1210</v>
+        <v>918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-215</v>
+        <v>-135</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1033</v>
+        <v>783</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1210</v>
+        <v>918</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-177</v>
+        <v>-135</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1368</v>
+        <v>783</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1210</v>
+        <v>918</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>158</v>
+        <v>-135</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>783</v>
+        <v>519</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-135</v>
+        <v>-249</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>783</v>
+        <v>554</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-135</v>
+        <v>-214</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>783</v>
+        <v>554</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-135</v>
+        <v>-214</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>943</v>
+        <v>554</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>918</v>
+        <v>1014</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>25</v>
+        <v>-460</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>745</v>
+        <v>604</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2094</v>
+        <v>1014</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1349</v>
+        <v>-410</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>745</v>
+        <v>604</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2094</v>
+        <v>1014</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1349</v>
+        <v>-410</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>793</v>
+        <v>554</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2094</v>
+        <v>1014</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1301</v>
+        <v>-460</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>834</v>
+        <v>604</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2094</v>
+        <v>1014</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-1260</v>
+        <v>-410</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-249</v>
+        <v>-410</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-214</v>
+        <v>-495</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-214</v>
+        <v>-495</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,33 +1541,1428 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>833</v>
+        <v>519</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>65</v>
+        <v>-495</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-335</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-511</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-510</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-410</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-495</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-664</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1363</v>
+        <v>1501</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>143</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1363</v>
+        <v>1353</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1358</v>
+        <v>1210</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1501</v>
+        <v>1368</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1358</v>
+        <v>1210</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1248</v>
+        <v>933</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1210</v>
+        <v>1358</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38</v>
+        <v>-425</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1368</v>
+        <v>1090</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1210</v>
+        <v>1358</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>158</v>
+        <v>-268</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>834</v>
+        <v>1138</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1085</v>
+        <v>1358</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-251</v>
+        <v>-220</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>835</v>
+        <v>1501</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1085</v>
+        <v>1358</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-250</v>
+        <v>143</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>995</v>
+        <v>590</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1085</v>
+        <v>918</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-90</v>
+        <v>-328</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>783</v>
+        <v>733</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-135</v>
+        <v>-185</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>783</v>
+        <v>943</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-135</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>519</v>
+        <v>745</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>768</v>
+        <v>2094</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-249</v>
+        <v>-1349</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>554</v>
+        <v>745</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>768</v>
+        <v>2094</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-214</v>
+        <v>-1349</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>554</v>
+        <v>793</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>768</v>
+        <v>2094</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-214</v>
+        <v>-1301</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>554</v>
+        <v>923</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1014</v>
+        <v>2094</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-460</v>
+        <v>-1171</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-410</v>
+        <v>-249</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-410</v>
+        <v>-214</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
         <v>554</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-460</v>
+        <v>-214</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-495</v>
+        <v>-410</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-495</v>
+        <v>-410</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-495</v>
+        <v>-410</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-511</v>
+        <v>-410</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>504</v>
+        <v>1103</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-510</v>
+        <v>89</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-410</v>
+        <v>-495</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-495</v>
+        <v>-511</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,26 +1860,26 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-129</v>
+        <v>-510</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-129</v>
+        <v>-410</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-94</v>
+        <v>-495</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-129</v>
+        <v>-495</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-129</v>
+        <v>-495</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-129</v>
+        <v>-94</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-44</v>
+        <v>-129</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-565</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-129</v>
+        <v>-55</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-129</v>
+        <v>-55</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-121</v>
+        <v>-129</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-94</v>
+        <v>-69</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>519</v>
+        <v>723</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-129</v>
+        <v>75</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>704</v>
+        <v>554</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-214</v>
+        <v>-94</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>46</v>
@@ -2597,9 +2597,9 @@
       <c r="I47" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>704</v>
+        <v>579</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-214</v>
+        <v>-69</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2642,9 +2642,9 @@
       <c r="I48" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>704</v>
+        <v>579</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-214</v>
+        <v>-69</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2687,9 +2687,9 @@
       <c r="I49" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>504</v>
+        <v>604</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-414</v>
+        <v>-44</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-414</v>
+        <v>-145</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-414</v>
+        <v>-121</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-414</v>
+        <v>-94</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,26 +2891,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-414</v>
+        <v>-145</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -2926,43 +2926,538 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-245</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-668</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D66" s="2" t="n">
         <v>519</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E66" s="2" t="n">
         <v>918</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F66" s="2" t="n">
         <v>-399</v>
       </c>
-      <c r="G55" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1353</v>
+        <v>1368</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1368</v>
+        <v>933</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1210</v>
+        <v>1358</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>158</v>
+        <v>-425</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>933</v>
+        <v>1090</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-425</v>
+        <v>-268</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1090</v>
+        <v>1138</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-268</v>
+        <v>-220</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1138</v>
+        <v>1501</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-220</v>
+        <v>143</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1501</v>
+        <v>590</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1358</v>
+        <v>918</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>143</v>
+        <v>-328</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>590</v>
+        <v>733</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-328</v>
+        <v>-185</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>733</v>
+        <v>783</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-185</v>
+        <v>-135</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>783</v>
+        <v>609</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>918</v>
+        <v>2094</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-135</v>
+        <v>-1485</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>943</v>
+        <v>642</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>918</v>
+        <v>2094</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>25</v>
+        <v>-1452</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>793</v>
+        <v>519</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2094</v>
+        <v>768</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1301</v>
+        <v>-249</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>923</v>
+        <v>554</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2094</v>
+        <v>768</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1171</v>
+        <v>-214</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-249</v>
+        <v>-214</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>554</v>
+        <v>833</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-214</v>
+        <v>65</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-214</v>
+        <v>-410</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>604</v>
+        <v>1103</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-410</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1103</v>
+        <v>604</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>89</v>
+        <v>-410</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-495</v>
+        <v>-410</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-495</v>
+        <v>-410</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>519</v>
+        <v>1103</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-495</v>
+        <v>89</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-511</v>
+        <v>-495</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-510</v>
+        <v>-495</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-410</v>
+        <v>-495</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-495</v>
+        <v>-511</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-495</v>
+        <v>-511</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-495</v>
+        <v>-511</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-129</v>
+        <v>-495</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-129</v>
+        <v>-495</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2147,9 +2147,9 @@
       <c r="I37" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-94</v>
+        <v>-495</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2192,9 +2192,9 @@
       <c r="I38" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>519</v>
+        <v>1103</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-129</v>
+        <v>89</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-565</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-55</v>
+        <v>-129</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-55</v>
+        <v>-129</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-69</v>
+        <v>-145</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>723</v>
+        <v>554</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>75</v>
+        <v>-94</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>flynas XY-565</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>554</v>
+        <v>593</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-94</v>
+        <v>-55</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>flynas XY-589</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-69</v>
+        <v>-55</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-69</v>
+        <v>-145</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-44</v>
+        <v>-69</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>527</v>
+        <v>673</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-121</v>
+        <v>25</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>503</v>
+        <v>593</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-145</v>
+        <v>-55</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>519</v>
+        <v>604</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-129</v>
+        <v>-44</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3033,10 +3033,10 @@
         <v>673</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-245</v>
+        <v>25</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>40</v>
@@ -3047,9 +3047,9 @@
       <c r="I57" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>704</v>
+        <v>519</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-214</v>
+        <v>-129</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,9 +3092,9 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>704</v>
+        <v>554</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-214</v>
+        <v>-94</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3137,9 +3137,9 @@
       <c r="I59" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,30 +3161,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-589</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>704</v>
+        <v>593</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-214</v>
+        <v>-55</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>504</v>
+        <v>593</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-414</v>
+        <v>-55</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-414</v>
+        <v>-145</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,26 +3296,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-569</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>504</v>
+        <v>593</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-414</v>
+        <v>-55</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,26 +3341,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>504</v>
+        <v>604</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-414</v>
+        <v>-44</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,26 +3386,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-414</v>
+        <v>-129</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -3421,43 +3421,1303 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>07-AUG-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-335</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-569</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-145</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-571</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-214</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-414</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>673</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-245</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-415</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-305</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-415</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-668</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D94" s="2" t="n">
         <v>519</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E94" s="2" t="n">
         <v>918</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F94" s="2" t="n">
         <v>-399</v>
       </c>
-      <c r="G66" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="G94" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1501</v>
+        <v>1363</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>143</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1368</v>
+        <v>1353</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1210</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>933</v>
+        <v>1368</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1358</v>
+        <v>1210</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-425</v>
+        <v>158</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1090</v>
+        <v>1003</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-268</v>
+        <v>-355</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1138</v>
+        <v>1090</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-220</v>
+        <v>-268</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1501</v>
+        <v>1138</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1358</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>143</v>
+        <v>-220</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-8224</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>590</v>
+        <v>1501</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>918</v>
+        <v>1358</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-328</v>
+        <v>143</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>flynas XY-573</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>783</v>
+        <v>733</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-135</v>
+        <v>-185</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-642</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>609</v>
+        <v>783</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2094</v>
+        <v>918</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1485</v>
+        <v>-135</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>642</v>
+        <v>943</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2094</v>
+        <v>918</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1452</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>745</v>
+        <v>641</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>2094</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1349</v>
+        <v>-1453</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>519</v>
+        <v>745</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>768</v>
+        <v>2094</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-249</v>
+        <v>-1349</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>554</v>
+        <v>793</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>768</v>
+        <v>2094</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-214</v>
+        <v>-1301</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-214</v>
+        <v>-249</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>833</v>
+        <v>554</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>768</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>65</v>
+        <v>-214</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-646</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>604</v>
+        <v>554</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-410</v>
+        <v>-214</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>604</v>
+        <v>833</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-410</v>
+        <v>65</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-410</v>
+        <v>-495</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1103</v>
+        <v>519</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>89</v>
+        <v>-495</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-410</v>
+        <v>-495</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>604</v>
+        <v>504</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-410</v>
+        <v>-510</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>604</v>
+        <v>504</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-410</v>
+        <v>-510</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1103</v>
+        <v>604</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>89</v>
+        <v>-410</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-511</v>
+        <v>-129</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>Saudia SV-335</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>503</v>
+        <v>579</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-511</v>
+        <v>-69</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-511</v>
+        <v>-145</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-495</v>
+        <v>-129</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
         <v>519</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-495</v>
+        <v>-129</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2147,9 +2147,9 @@
       <c r="I37" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>flynas XY-565</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-495</v>
+        <v>-55</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>flynas XY-571</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1103</v>
+        <v>593</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>89</v>
+        <v>-55</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>40</v>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-567</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>519</v>
+        <v>593</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-129</v>
+        <v>-55</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-145</v>
+        <v>-94</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-307</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>503</v>
+        <v>579</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-145</v>
+        <v>-69</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-145</v>
+        <v>-44</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-94</v>
+        <v>-129</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-565</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>593</v>
+        <v>723</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-55</v>
+        <v>75</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>40</v>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>07-AUG-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-589</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>593</v>
+        <v>673</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-55</v>
+        <v>25</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>40</v>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-305</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>579</v>
+        <v>527</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-69</v>
+        <v>-121</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-129</v>
+        <v>-94</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>519</v>
+        <v>673</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-129</v>
+        <v>25</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,30 +2936,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>593</v>
+        <v>704</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-55</v>
+        <v>-214</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>604</v>
+        <v>704</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-44</v>
+        <v>-214</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>25</v>
+        <v>-214</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-129</v>
+        <v>-414</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-94</v>
+        <v>-414</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-589</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>593</v>
+        <v>504</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-55</v>
+        <v>-414</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>593</v>
+        <v>673</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-55</v>
+        <v>-245</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>40</v>
@@ -3227,9 +3227,9 @@
       <c r="I61" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
         <v>503</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-145</v>
+        <v>-415</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3272,9 +3272,9 @@
       <c r="I62" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,30 +3296,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-569</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-55</v>
+        <v>-399</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,1383 +3341,33 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flynas XY-565</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-44</v>
+        <v>-325</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>05-AUG-26</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-644</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>-129</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>07-AUG-26</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-307</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>07-AUG-26</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-305</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>07-AUG-26</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-335</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-644</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>527</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>-121</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>554</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>-94</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>554</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>-94</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>11-AUG-26</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-301</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>11-AUG-26</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-644</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>554</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>-94</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>11-AUG-26</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-569</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>12-AUG-26</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-305</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>14-AUG-26</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-387</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>14-AUG-26</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-571</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>14-AUG-26</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-577</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>-129</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-565</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-571</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>673</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>-245</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-309</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>-415</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-305</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>-415</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-668</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>-399</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1363</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1358</v>
+        <v>2094</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>-1694</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1353</v>
+        <v>486</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1210</v>
+        <v>2094</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>143</v>
+        <v>-1608</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1368</v>
+        <v>486</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1210</v>
+        <v>2094</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>158</v>
+        <v>-1608</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1003</v>
+        <v>853</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1358</v>
+        <v>2094</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-355</v>
+        <v>-1241</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>40</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1090</v>
+        <v>486</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1358</v>
+        <v>708</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-268</v>
+        <v>-222</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1138</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1358</v>
+        <v>768</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-220</v>
+        <v>-368</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8224</t>
+          <t>Nile Air NP-228</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1501</v>
+        <v>486</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1358</v>
+        <v>768</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>143</v>
+        <v>-282</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-656</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>733</v>
+        <v>556</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>918</v>
+        <v>768</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-185</v>
+        <v>-212</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,28 +911,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-573</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>733</v>
+        <v>791</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-185</v>
+        <v>-127</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-642</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-135</v>
+        <v>-127</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>943</v>
+        <v>791</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>918</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>25</v>
+        <v>-127</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>641</v>
+        <v>901</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2094</v>
+        <v>1128</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1453</v>
+        <v>-227</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>745</v>
+        <v>901</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2094</v>
+        <v>1128</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1349</v>
+        <v>-227</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>745</v>
+        <v>901</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2094</v>
+        <v>1128</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1349</v>
+        <v>-227</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>793</v>
+        <v>691</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2094</v>
+        <v>1014</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1301</v>
+        <v>-323</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>519</v>
+        <v>691</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-249</v>
+        <v>-323</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1247,7 +1247,7 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>554</v>
+        <v>691</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-214</v>
+        <v>-323</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1292,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-646</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>554</v>
+        <v>641</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-214</v>
+        <v>-373</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>833</v>
+        <v>641</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>768</v>
+        <v>1014</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>65</v>
+        <v>-373</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-410</v>
+        <v>-373</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-410</v>
+        <v>-458</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,7 +1472,7 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-410</v>
+        <v>-458</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1014</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-495</v>
+        <v>-458</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1562,7 +1562,7 @@
       <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-301</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-495</v>
+        <v>-145</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-495</v>
+        <v>-92</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1652,9 +1652,9 @@
       <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-510</v>
+        <v>-92</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>504</v>
+        <v>591</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-510</v>
+        <v>-57</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-410</v>
+        <v>-92</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-495</v>
+        <v>-92</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1832,9 +1832,9 @@
       <c r="I30" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-495</v>
+        <v>-92</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1877,9 +1877,9 @@
       <c r="I31" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-662</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1014</v>
+        <v>648</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-495</v>
+        <v>-92</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>Saudia SV-309</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,7 +1967,7 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-335</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>579</v>
+        <v>503</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-69</v>
+        <v>-145</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,7 +2012,7 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>503</v>
+        <v>641</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-145</v>
+        <v>-7</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,7 +2057,7 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-129</v>
+        <v>-92</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,7 +2102,7 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-129</v>
+        <v>-92</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2147,7 +2147,7 @@
       <c r="I37" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-565</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>593</v>
+        <v>788</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-55</v>
+        <v>140</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>40</v>
@@ -2192,7 +2192,7 @@
       <c r="I38" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-571</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-55</v>
+        <v>-57</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,28 +2261,28 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-567</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-55</v>
+        <v>-92</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>519</v>
+        <v>738</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-129</v>
+        <v>90</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>Saudia SV-383</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2372,7 +2372,7 @@
       <c r="I42" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>Saudia SV-387</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>554</v>
+        <v>503</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-94</v>
+        <v>-145</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
@@ -2417,7 +2417,7 @@
       <c r="I43" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-69</v>
+        <v>-92</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2462,7 +2462,7 @@
       <c r="I44" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-44</v>
+        <v>-57</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2507,7 +2507,7 @@
       <c r="I45" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>14-AUG-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>519</v>
+        <v>591</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-129</v>
+        <v>-57</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2552,7 +2552,7 @@
       <c r="I46" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>723</v>
+        <v>556</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>75</v>
+        <v>-92</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>07-AUG-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>673</v>
+        <v>319</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>25</v>
+        <v>-599</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,28 +2666,28 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>503</v>
+        <v>409</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-145</v>
+        <v>-509</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>25-SEP-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,28 +2711,28 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>flyadeal F3-753</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>527</v>
+        <v>409</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-121</v>
+        <v>-509</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,28 +2756,28 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>Air Arabia Egypt E5-328</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-94</v>
+        <v>-439</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>673</v>
+        <v>556</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>25</v>
+        <v>-362</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>26-SEP-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,528 +2846,33 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>flyadeal F3-755</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>673</v>
+        <v>586</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>648</v>
+        <v>918</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>25</v>
+        <v>-332</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>648</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>-129</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>704</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-672</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-674</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-670</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>-414</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>25-SEP-26</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-581</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>673</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>-245</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-383</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>503</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>-415</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-668</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>519</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>-399</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-565</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>918</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>-325</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_JED_HMB_threats.xlsx
+++ b/excel_routes/route_JED_HMB_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-171</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>400</v>
+        <v>495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2094</v>
+        <v>1128</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1694</v>
+        <v>-633</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>486</v>
+        <v>601</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2094</v>
+        <v>1128</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1608</v>
+        <v>-527</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>486</v>
+        <v>769</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2094</v>
+        <v>1128</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1608</v>
+        <v>-359</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>Saudia SV-301</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>853</v>
+        <v>496</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2094</v>
+        <v>533</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1241</v>
+        <v>-37</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-128</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>708</v>
+        <v>533</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-222</v>
+        <v>-37</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-173</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>400</v>
+        <v>496</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>768</v>
+        <v>533</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-368</v>
+        <v>-37</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-228</t>
+          <t>Saudia SV-301</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>768</v>
+        <v>498</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-282</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-656</t>
+          <t>Saudia SV-307</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>556</v>
+        <v>496</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>768</v>
+        <v>498</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-212</v>
+        <v>-2</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Saudia SV-305</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>791</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>918</v>
+        <v>498</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-127</v>
+        <v>-2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Nesma Airlines NE-173</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>791</v>
+        <v>400</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>918</v>
+        <v>463</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-127</v>
+        <v>-63</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>791</v>
+        <v>493</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>918</v>
+        <v>463</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-127</v>
+        <v>30</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>Nile Air NP-128</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>901</v>
+        <v>399</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1128</v>
+        <v>463</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-227</v>
+        <v>-64</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>Nesma Airlines NE-171</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>901</v>
+        <v>400</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1128</v>
+        <v>463</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-227</v>
+        <v>-63</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>Saudia SV-389</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>901</v>
+        <v>496</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1128</v>
+        <v>463</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-227</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-666</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>691</v>
+        <v>634</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1014</v>
+        <v>918</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-323</v>
+        <v>-284</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,7 +1202,7 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1014</v>
+        <v>918</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-323</v>
+        <v>-218</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1247,7 +1247,7 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1014</v>
+        <v>918</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-323</v>
+        <v>-218</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1292,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1014</v>
+        <v>708</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-373</v>
+        <v>-74</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,9 +1337,9 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>641</v>
+        <v>700</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1014</v>
+        <v>708</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-373</v>
+        <v>-8</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>641</v>
+        <v>700</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1014</v>
+        <v>708</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-373</v>
+        <v>-8</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>556</v>
+        <v>700</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-458</v>
+        <v>-68</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-664</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>556</v>
+        <v>769</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-458</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-666</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>556</v>
+        <v>769</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1014</v>
+        <v>768</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-458</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-301</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>503</v>
+        <v>769</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>648</v>
+        <v>768</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-145</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,7 +1607,7 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>556</v>
+        <v>769</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>648</v>
+        <v>768</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-92</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1652,7 +1652,7 @@
       <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>556</v>
+        <v>769</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>648</v>
+        <v>768</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-92</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1697,7 +1697,7 @@
       <c r="I27" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>591</v>
+        <v>634</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>648</v>
+        <v>768</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-57</v>
+        <v>-134</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1742,7 +1742,7 @@
       <c r="I28" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>648</v>
+        <v>768</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-92</v>
+        <v>-134</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1787,7 +1787,7 @@
       <c r="I29" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>648</v>
+        <v>768</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-92</v>
+        <v>-134</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1832,7 +1832,7 @@
       <c r="I30" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1860,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>556</v>
+        <v>604</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-92</v>
+        <v>-410</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1877,9 +1877,9 @@
       <c r="I31" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>556</v>
+        <v>604</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-92</v>
+        <v>-410</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-309</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-145</v>
+        <v>-410</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-145</v>
+        <v>-470</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>641</v>
+        <v>544</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-7</v>
+        <v>-470</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-670</t>
+          <t>EgyptAir MS-664</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-92</v>
+        <v>-470</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-92</v>
+        <v>-521</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2147,9 +2147,9 @@
       <c r="I37" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>788</v>
+        <v>514</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>140</v>
+        <v>-500</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-57</v>
+        <v>-500</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2237,9 +2237,9 @@
       <c r="I39" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-674</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-92</v>
+        <v>-521</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>46</v>
@@ -2282,9 +2282,9 @@
       <c r="I40" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-581</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>738</v>
+        <v>514</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>90</v>
+        <v>-500</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-383</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-145</v>
+        <v>-500</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2372,9 +2372,9 @@
       <c r="I42" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-387</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>503</v>
+        <v>793</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>648</v>
+        <v>1014</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-145</v>
+        <v>-221</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08-AUG-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-92</v>
+        <v>-155</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2462,7 +2462,7 @@
       <c r="I44" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-644</t>
+          <t>EgyptAir MS-662</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-57</v>
+        <v>-155</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2507,7 +2507,7 @@
       <c r="I45" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>14-AUG-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-674</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>591</v>
+        <v>514</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-57</v>
+        <v>-134</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2552,7 +2552,7 @@
       <c r="I46" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>15-AUG-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-672</t>
+          <t>flynas XY-581</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>556</v>
+        <v>793</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>648</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-92</v>
+        <v>145</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>319</v>
+        <v>493</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-599</v>
+        <v>-155</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,28 +2666,28 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-755</t>
+          <t>EgyptAir MS-668</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>409</v>
+        <v>514</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-509</v>
+        <v>-134</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25-SEP-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,28 +2711,28 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-753</t>
+          <t>EgyptAir MS-644</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>409</v>
+        <v>514</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-509</v>
+        <v>-134</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,28 +2756,28 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-328</t>
+          <t>EgyptAir MS-672</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-439</v>
+        <v>-155</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-668</t>
+          <t>EgyptAir MS-670</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>556</v>
+        <v>493</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>918</v>
+        <v>648</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-362</v>
+        <v>-155</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,43 +2836,2023 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-666</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-134</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-662</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>544</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>544</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-134</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-152</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>01-AUG-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-670</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-152</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>08-AUG-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-644</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-581</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-152</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>14-AUG-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-674</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>554</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-152</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>15-AUG-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-672</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>22-AUG-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>22-AUG-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>26-AUG-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-309</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>28-AUG-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-383</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-387</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>29-AUG-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-389</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>18-SEP-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-307</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-128</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-432</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-755</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-332</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>25-SEP-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-565</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-305</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>26-SEP-26</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SM-454</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-755</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>586</v>
-      </c>
-      <c r="E53" s="2" t="n">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-301</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E95" s="2" t="n">
         <v>918</v>
       </c>
-      <c r="F53" s="2" t="n">
-        <v>-332</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="F95" s="2" t="n">
+        <v>-422</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-668</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-399</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-454</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-577</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-305</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
